--- a/DB設計.xlsx
+++ b/DB設計.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/72d4f8b8821e93b1/デスクトップ/アンドロイド開発/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="6_{55F0AA7E-EEF7-437D-8935-AA4E2E59651E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{5FED6FC1-B7BD-4CF7-8E8D-5304129E691D}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="6_{55F0AA7E-EEF7-437D-8935-AA4E2E59651E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C6EC8882-AF2A-4DDD-9FF7-33632E0E339E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8844" xr2:uid="{62A4FDF6-86DA-473D-8BB1-34516B904261}"/>
   </bookViews>
@@ -25,13 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>Deck</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　　　　デッキ管理　　　　　　　　（作成/編集/削除/色分け）</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -267,14 +263,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1対多</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1　　　　　　多</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -299,85 +287,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デッキのテーマカラー(#RRGGBB形式) — デフォルト値設定を推奨</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　　デッキの名前 　　　　　デッキ名 — NOT NULL制約　を推奨</t>
-    <rPh sb="6" eb="8">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デッキの説明文ーNULLABLEで　問題なし</t>
-    <rPh sb="4" eb="7">
-      <t>セツメイブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作成日時ーDEFAULT NOW() を設定すること</t>
-    <rPh sb="0" eb="2">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ニチジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve">  単語登録/単語一覧/弱点分析（correctCount /missCount）</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>deckId</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FK（外部キー）ON DELETE CASCADE を追加 — デッキ   削除時に紐づく単語も自動削除し、孤立データを防ぐ</t>
-    <rPh sb="3" eb="5">
-      <t>ガイブ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>NOT NULL 制約を追加 — 意味が空の単語は4択クイズの選択肢生成ができない</t>
-    <rPh sb="9" eb="11">
-      <t>セイヤク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イミ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ソラ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>タンゴ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>タク</t>
-    </rPh>
-    <rPh sb="31" eb="34">
-      <t>センタクシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>セイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>NOT NULL 制約を追加 —        単語名が空の登録を防ぐ       （画面でも必須項目）</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -428,11 +342,81 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ON DELETE CASCADE を追加  デッキ削除時にプレイ履歴も削除し整合性を保つ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ENUM型 or CHECK制約を追加  例: 'quiz' ・ 'timeattack' ・ 'weak'。不正な値の挿入を防ぐ</t>
+    <t>scoreMultiplier</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弱点分析(問題ごとの正誤歴）   結果画面の間違い一覧</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  4択クイズ/タイムアタック/    コンボシステム/ランキング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>selectedAnswer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TEXT NULLABLE を新規追加 ユーザーが選んだ選択肢を保存。結果画面の「間違えた単語」で「何を選んだか」を表示できるようになる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1対多</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　   　デッキ管理　　 　　　　　   　　（作成/編集/削除/色分け）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　デッキの名前 　　　                     デッキ名 — NOT NULL制約　を推奨</t>
+    <rPh sb="6" eb="8">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デッキの説明文ーNULLABLEで問題なし</t>
+    <rPh sb="4" eb="7">
+      <t>セツメイブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デッキのテーマカラー(#RRGGBB形式)    デフォルト値設定を推奨</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作成日時DEFAULT NOW() を設定すること</t>
+    <rPh sb="0" eb="2">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FK(外部キー)ON DELETE CASCADEを追加QuizResult  削除時にログも連動削除</t>
+    <rPh sb="3" eb="5">
+      <t>ガイブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FK(外部キー)ON DELETE CASCADEを追加        単語削除時に回答ログも連動削除</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ON DELETE CASCADE を追加デッキ    削除時にプレイ履歴も削除し整合性を保つ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ENUM型 or CHECK制約を追加             例: 'quiz'・'timeattack'・'weak'              不正な値の挿入を防ぐ</t>
     <rPh sb="4" eb="5">
       <t>ガタ</t>
     </rPh>
@@ -442,56 +426,64 @@
     <rPh sb="17" eb="19">
       <t>ツイカ</t>
     </rPh>
-    <rPh sb="21" eb="22">
+    <rPh sb="32" eb="33">
       <t>レイ</t>
     </rPh>
-    <rPh sb="55" eb="57">
+    <rPh sb="75" eb="77">
       <t>フセイ</t>
     </rPh>
-    <rPh sb="58" eb="59">
+    <rPh sb="78" eb="79">
       <t>アタイ</t>
     </rPh>
-    <rPh sb="60" eb="62">
+    <rPh sb="80" eb="82">
       <t>ソウニュウ</t>
     </rPh>
-    <rPh sb="63" eb="64">
+    <rPh sb="83" eb="84">
       <t>フセ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>scoreMultiplier</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>REAL DEFAULT 1.0 を新規追加 画面に「倍率 ×1.5」表示があるが保存されていない。結果画面の再表示・ランキングでの倍率表示に必要</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FK(外部キー)ON DELETE CASCADE を追加 QuizResult  削除時にログも連動削除</t>
+    <t>NOT NULL 制約を追加意味が空の単語は4択クイズの選択肢生成ができない</t>
+    <rPh sb="9" eb="11">
+      <t>セイヤク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ソラ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>タク</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NOT NULL 制約を追加単語名が空の登録を防ぐ（画面でも必須項目）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FK（外部キー）ON DELETE CASCADE を追加デッキ削除時に紐づく単語も自動削除し、孤立データを防ぐ</t>
     <rPh sb="3" eb="5">
       <t>ガイブ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>FK(外部キー)ON DELETE CASCADE を追加 — 単語削除時に回答ログも連動削除</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弱点分析(問題ごとの正誤歴）   結果画面の間違い一覧</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  4択クイズ/タイムアタック/    コンボシステム/ランキング</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>selectedAnswer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>TEXT NULLABLE を新規追加 ユーザーが選んだ選択肢を保存。結果画面の「間違えた単語」で「何を選んだか」を表示できるようになる</t>
+    <t>REAL DEFAULT1.0を新規追加画面に「倍率×1.5」表示があるが保存されていない。結果画面の再表示・ランキングでの倍率表示に必要</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -499,7 +491,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,6 +507,46 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -927,7 +959,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -940,184 +972,229 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1141,16 +1218,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>18587</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>15551</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>7249</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>18586</xdr:colOff>
+      <xdr:colOff>18587</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>18586</xdr:rowOff>
+      <xdr:rowOff>18587</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1165,8 +1242,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="4702099" y="1865786"/>
-          <a:ext cx="2676292" cy="475971"/>
+          <a:off x="5489510" y="2006083"/>
+          <a:ext cx="2009118" cy="765035"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1254,23 +1331,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>3160</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>5575</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>341644</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>364253</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>3160</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>205739</xdr:rowOff>
+      <xdr:colOff>307731</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
+        <xdr:cNvPr id="32" name="直線コネクタ 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{991A88C7-BC67-41E2-A0E4-43104BE22591}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25F60CF6-1596-4A62-B49E-BEFD9A1CA83B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1278,8 +1355,228 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9370184" y="8164551"/>
-          <a:ext cx="0" cy="906408"/>
+          <a:off x="7873721" y="9434984"/>
+          <a:ext cx="640164" cy="16747"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>355880</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>337038</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>351692</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>347924</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="直線コネクタ 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3AEBBAF-90BC-40A3-8975-FA121FB241DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7887957" y="11503269"/>
+          <a:ext cx="669889" cy="10886"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>301030</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>327828</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>333688</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="直線コネクタ 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE2189C7-DA9B-40F7-8A7D-10FF9B537532}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7833107" y="10790674"/>
+          <a:ext cx="706735" cy="10886"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>307731</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>322383</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>348343</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="36" name="直線コネクタ 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58BAFEC4-A9F4-4FC0-AF88-93E3ED1C6742}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7839808" y="10169768"/>
+          <a:ext cx="714689" cy="1"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>15551</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>413289</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>25831</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68840D59-34FE-42BD-A065-FD3A2488E8C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12269755" y="2730391"/>
+          <a:ext cx="1347668" cy="22140"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1310,23 +1607,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>13138</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>249621</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>46653</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>450979</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>643759</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>105104</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>400373</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="18" name="コネクタ: カギ線 17">
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD4829C0-3EC1-4C6A-8A2B-D936AFD06AE2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7A2C891-EDC9-4646-8B5C-E4C1A40FFF0A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1334,30 +1631,23 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4821621" y="8198069"/>
-          <a:ext cx="2640724" cy="2338552"/>
+          <a:off x="5520612" y="7977673"/>
+          <a:ext cx="7133965" cy="15551"/>
         </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
-          </a:avLst>
+        <a:prstGeom prst="line">
+          <a:avLst/>
         </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
+        <a:ln w="38100"/>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="tx1"/>
@@ -1368,23 +1658,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>283028</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>217714</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>374542</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>315686</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>374542</xdr:colOff>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="直線コネクタ 31">
+        <xdr:cNvPr id="21" name="直線コネクタ 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25F60CF6-1596-4A62-B49E-BEFD9A1CA83B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3C9D0EA-2325-4BE7-AC9C-8880EDDD8B1A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1392,27 +1682,23 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2307771" y="8904514"/>
-          <a:ext cx="707572" cy="10886"/>
+          <a:off x="12669864" y="3396712"/>
+          <a:ext cx="0" cy="4584915"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
+        <a:ln w="38100"/>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="tx1"/>
@@ -1423,161 +1709,49 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>326573</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>10886</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>374542</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>297051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>359231</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>21772</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>51661</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>309966</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="34" name="直線コネクタ 33">
+        <xdr:cNvPr id="23" name="直線矢印コネクタ 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3AEBBAF-90BC-40A3-8975-FA121FB241DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76E4BF10-32E6-40D0-B22D-E56C099F5AC1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2351316" y="10308772"/>
-          <a:ext cx="707572" cy="10886"/>
+        <a:xfrm flipV="1">
+          <a:off x="12669864" y="3370882"/>
+          <a:ext cx="1020305" cy="12915"/>
         </a:xfrm>
-        <a:prstGeom prst="line">
+        <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>315684</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>195943</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>348342</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>206829</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="35" name="直線コネクタ 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE2189C7-DA9B-40F7-8A7D-10FF9B537532}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2340427" y="9808029"/>
-          <a:ext cx="707572" cy="10886"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>315685</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>348343</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="36" name="直線コネクタ 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58BAFEC4-A9F4-4FC0-AF88-93E3ED1C6742}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2340428" y="9372599"/>
-          <a:ext cx="707572" cy="10886"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="tx1"/>
@@ -1886,831 +2060,873 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEA3E178-BFF4-4CD1-BDA5-2E9B6DBF0AB3}">
-  <dimension ref="B1:X55"/>
+  <dimension ref="B1:AA55"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="7" max="7" width="10.3984375" customWidth="1"/>
     <col min="15" max="15" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.45">
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:27" x14ac:dyDescent="0.45">
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="2:17" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="17" t="s">
+    <row r="4" spans="2:27" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="24"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="24"/>
       <c r="I4" s="3"/>
       <c r="J4" s="1"/>
-      <c r="L4" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="18"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="63"/>
-    </row>
-    <row r="5" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="20"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="3"/>
+      <c r="L4" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="26"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="24"/>
+      <c r="U4" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="V4" s="26"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y4" s="23"/>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="24"/>
+    </row>
+    <row r="5" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="60"/>
       <c r="I5" s="3"/>
       <c r="J5" s="1"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="58"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="40"/>
       <c r="P5" s="59"/>
-      <c r="Q5" s="60"/>
-    </row>
-    <row r="6" spans="2:17" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="3"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="60"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="40"/>
+      <c r="Y5" s="59"/>
+      <c r="Z5" s="59"/>
+      <c r="AA5" s="60"/>
+    </row>
+    <row r="6" spans="2:27" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="3"/>
       <c r="J6" s="1"/>
-      <c r="L6" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="M6" s="18"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="48"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="3"/>
+      <c r="L6" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="26"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="27"/>
+      <c r="U6" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6" s="26"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="26"/>
+      <c r="Z6" s="26"/>
+      <c r="AA6" s="27"/>
+    </row>
+    <row r="7" spans="2:27" x14ac:dyDescent="0.45">
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="37"/>
       <c r="I7" s="3"/>
       <c r="J7" s="1"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="44"/>
-    </row>
-    <row r="8" spans="2:17" ht="29.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="3"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="29"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="29"/>
+    </row>
+    <row r="8" spans="2:27" ht="29.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="15"/>
       <c r="I8" s="3"/>
       <c r="J8" s="1"/>
-      <c r="L8" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="39"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="51"/>
-    </row>
-    <row r="9" spans="2:17" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="3"/>
+      <c r="L8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="59"/>
+      <c r="Q8" s="59"/>
+      <c r="R8" s="60"/>
+      <c r="U8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="V8" s="5"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y8" s="59"/>
+      <c r="Z8" s="59"/>
+      <c r="AA8" s="60"/>
+    </row>
+    <row r="9" spans="2:27" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
       <c r="I9" s="3"/>
       <c r="J9" s="1"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="54"/>
-    </row>
-    <row r="10" spans="2:17" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="38" t="s">
+      <c r="L9" s="7"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="59"/>
+      <c r="Q9" s="59"/>
+      <c r="R9" s="60"/>
+      <c r="S9" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="U9" s="7"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="40"/>
+      <c r="Y9" s="59"/>
+      <c r="Z9" s="59"/>
+      <c r="AA9" s="60"/>
+    </row>
+    <row r="10" spans="2:27" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="15"/>
+      <c r="L10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="68"/>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="69"/>
+      <c r="S10" s="34"/>
+      <c r="U10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V10" s="5"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="70" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y10" s="71"/>
+      <c r="Z10" s="71"/>
+      <c r="AA10" s="72"/>
+    </row>
+    <row r="11" spans="2:27" ht="25.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="2"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="73"/>
+      <c r="Y11" s="74"/>
+      <c r="Z11" s="74"/>
+      <c r="AA11" s="75"/>
+    </row>
+    <row r="12" spans="2:27" ht="25.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51"/>
-      <c r="L10" s="38" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="15"/>
+      <c r="L12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M10" s="39"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="51"/>
-    </row>
-    <row r="11" spans="2:17" ht="25.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="54"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="54"/>
-    </row>
-    <row r="12" spans="2:17" ht="25.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="38" t="s">
+      <c r="M12" s="5"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="2"/>
+      <c r="U12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="V12" s="5"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y12" s="68"/>
+      <c r="Z12" s="68"/>
+      <c r="AA12" s="69"/>
+    </row>
+    <row r="13" spans="2:27" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="37"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="76"/>
+      <c r="Y13" s="77"/>
+      <c r="Z13" s="77"/>
+      <c r="AA13" s="78"/>
+    </row>
+    <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="51"/>
-      <c r="L12" s="38" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="15"/>
+      <c r="L14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M12" s="39"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="41" t="s">
+      <c r="M14" s="5"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="42"/>
-    </row>
-    <row r="13" spans="2:17" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="29"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="54"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="44"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B14" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="L14" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="M14" s="39"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="42"/>
-    </row>
-    <row r="15" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="60"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="44"/>
-    </row>
-    <row r="16" spans="2:17" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="33"/>
+      <c r="U14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="5"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="33"/>
+    </row>
+    <row r="15" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="37"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="36"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="37"/>
+    </row>
+    <row r="16" spans="2:27" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="D16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="L16" s="38" t="s">
+      <c r="L16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="33"/>
+      <c r="U16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V16" s="5"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="33"/>
+    </row>
+    <row r="17" spans="2:27" x14ac:dyDescent="0.45">
+      <c r="D17" s="3"/>
+      <c r="E17" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" s="7"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="29"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="36"/>
+      <c r="Z17" s="36"/>
+      <c r="AA17" s="37"/>
+    </row>
+    <row r="18" spans="2:27" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E18" s="34"/>
+      <c r="L18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="41" t="s">
+      <c r="M18" s="5"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="42"/>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="D17" s="3"/>
-      <c r="E17" s="57" t="s">
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="33"/>
+      <c r="U18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="V18" s="5"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="15"/>
+    </row>
+    <row r="19" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="L19" s="7"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="37"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="40"/>
+      <c r="Y19" s="59"/>
+      <c r="Z19" s="59"/>
+      <c r="AA19" s="60"/>
+    </row>
+    <row r="20" spans="2:27" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="26"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="24"/>
+      <c r="L20" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="63"/>
+      <c r="U20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V20" s="5"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="15"/>
+    </row>
+    <row r="21" spans="2:27" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="60"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="66"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="40"/>
+      <c r="Y21" s="59"/>
+      <c r="Z21" s="59"/>
+      <c r="AA21" s="60"/>
+    </row>
+    <row r="22" spans="2:27" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="26"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="27"/>
+      <c r="L22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="15"/>
+      <c r="U22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="V22" s="5"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="15"/>
+    </row>
+    <row r="23" spans="2:27" x14ac:dyDescent="0.45">
+      <c r="B23" s="7"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="37"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="21"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="19"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="21"/>
+    </row>
+    <row r="24" spans="2:27" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="63"/>
+      <c r="L24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="33"/>
+      <c r="U24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="5"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5"/>
+      <c r="AA24" s="33"/>
+    </row>
+    <row r="25" spans="2:27" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B25" s="7"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="66"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="39"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="12"/>
+      <c r="X25" s="38"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="39"/>
+    </row>
+    <row r="26" spans="2:27" ht="37.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="63"/>
+    </row>
+    <row r="27" spans="2:27" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="66"/>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="2:27" ht="16.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="37"/>
+      <c r="J28" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="45"/>
+      <c r="L28" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="M28" s="50"/>
+      <c r="N28" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="L17" s="29"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="44"/>
-    </row>
-    <row r="18" spans="2:24" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E18" s="57"/>
-      <c r="L18" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="M18" s="39"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="42"/>
-    </row>
-    <row r="19" spans="2:24" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="L19" s="29"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="44"/>
-    </row>
-    <row r="20" spans="2:24" ht="43.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="62"/>
-      <c r="G20" s="63"/>
-      <c r="L20" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="51"/>
-    </row>
-    <row r="21" spans="2:24" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="20"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="60"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="54"/>
-    </row>
-    <row r="22" spans="2:24" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="47" t="s">
+      <c r="O28" s="50"/>
+      <c r="P28" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="S28" s="43"/>
+    </row>
+    <row r="29" spans="2:27" ht="19.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B29" s="7"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="37"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="41"/>
+    </row>
+    <row r="30" spans="2:27" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="63"/>
+      <c r="L30" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="M30" s="48"/>
+      <c r="N30" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="O30" s="48"/>
+      <c r="P30" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="48"/>
-      <c r="L22" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="P22" s="50"/>
-      <c r="Q22" s="51"/>
-    </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="44"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="52"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="54"/>
-    </row>
-    <row r="24" spans="2:24" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="50"/>
-      <c r="G24" s="51"/>
-      <c r="L24" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="41" t="s">
+      <c r="Q30" s="48"/>
+      <c r="R30" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="S30" s="41"/>
+    </row>
+    <row r="31" spans="2:27" ht="26.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="7"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="66"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="40"/>
+      <c r="S31" s="41"/>
+    </row>
+    <row r="32" spans="2:27" ht="16.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="37"/>
+      <c r="L32" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="M32" s="48"/>
+      <c r="N32" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="O32" s="48"/>
+      <c r="P32" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q32" s="48"/>
+      <c r="R32" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="S32" s="41"/>
+    </row>
+    <row r="33" spans="2:19" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="39"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="48"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="48"/>
+      <c r="R33" s="40"/>
+      <c r="S33" s="41"/>
+    </row>
+    <row r="34" spans="2:19" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="L34" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="42"/>
-    </row>
-    <row r="25" spans="2:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B25" s="29"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="54"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="46"/>
-    </row>
-    <row r="26" spans="2:24" ht="37.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="50"/>
-      <c r="G26" s="51"/>
-    </row>
-    <row r="27" spans="2:24" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="29"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="54"/>
-      <c r="O27" s="57" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="2:24" ht="27.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="42"/>
-      <c r="O28" s="57"/>
-    </row>
-    <row r="29" spans="2:24" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B29" s="29"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="44"/>
-    </row>
-    <row r="30" spans="2:24" ht="45" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B30" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" s="50"/>
-      <c r="G30" s="51"/>
-      <c r="L30" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M30" s="18"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="25"/>
-    </row>
-    <row r="31" spans="2:24" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="29"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="54"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="28"/>
-      <c r="X31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="2:24" ht="37.799999999999997" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="39"/>
-      <c r="G32" s="42"/>
-      <c r="L32" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="M32" s="18"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="48"/>
-    </row>
-    <row r="33" spans="2:17" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="20"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="46"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="44"/>
-    </row>
-    <row r="34" spans="2:17" ht="26.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="L34" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="M34" s="39"/>
-      <c r="N34" s="40"/>
-      <c r="O34" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="P34" s="50"/>
-      <c r="Q34" s="51"/>
-    </row>
-    <row r="35" spans="2:17" ht="28.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L35" s="29"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="31"/>
+      <c r="M34" s="48"/>
+      <c r="N34" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="O34" s="48"/>
+      <c r="P34" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q34" s="48"/>
+      <c r="R34" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="S34" s="41"/>
+    </row>
+    <row r="35" spans="2:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="L35" s="56"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="51"/>
       <c r="O35" s="52"/>
-      <c r="P35" s="53"/>
-      <c r="Q35" s="54"/>
-    </row>
-    <row r="36" spans="2:17" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L36" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" s="39"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="P36" s="50"/>
-      <c r="Q36" s="51"/>
-    </row>
-    <row r="37" spans="2:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B37" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="35"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="52"/>
-      <c r="P37" s="53"/>
-      <c r="Q37" s="54"/>
-    </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B38" s="36"/>
-      <c r="C38" s="37"/>
-      <c r="H38" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="I38" s="33"/>
-      <c r="L38" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="M38" s="39"/>
-      <c r="N38" s="40"/>
-      <c r="O38" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="51"/>
-    </row>
-    <row r="39" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="H39" s="13"/>
-      <c r="I39" s="14"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="52"/>
-      <c r="P39" s="53"/>
-      <c r="Q39" s="54"/>
-    </row>
-    <row r="40" spans="2:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="9"/>
-      <c r="H40" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="I40" s="14"/>
-      <c r="L40" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" s="39"/>
-      <c r="N40" s="40"/>
-      <c r="O40" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="P40" s="39"/>
-      <c r="Q40" s="42"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B41" s="4"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="43"/>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="44"/>
-    </row>
-    <row r="42" spans="2:17" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="14"/>
-      <c r="L42" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="39"/>
-      <c r="N42" s="40"/>
-      <c r="O42" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="P42" s="39"/>
-      <c r="Q42" s="42"/>
-    </row>
-    <row r="43" spans="2:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B43" s="4"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="31"/>
-      <c r="O43" s="43"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="44"/>
-    </row>
-    <row r="44" spans="2:17" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G44" s="5"/>
-      <c r="H44" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I44" s="14"/>
-      <c r="L44" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="M44" s="39"/>
-      <c r="N44" s="40"/>
-      <c r="O44" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="P44" s="50"/>
-      <c r="Q44" s="51"/>
-    </row>
-    <row r="45" spans="2:17" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B45" s="4"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="16"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="31"/>
-      <c r="O45" s="52"/>
-      <c r="P45" s="53"/>
-      <c r="Q45" s="54"/>
-    </row>
-    <row r="46" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B46" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G46" s="5"/>
-      <c r="L46" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="M46" s="39"/>
-      <c r="N46" s="40"/>
-      <c r="O46" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="P46" s="50"/>
-      <c r="Q46" s="51"/>
-    </row>
-    <row r="47" spans="2:17" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="6"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="7"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="52"/>
-      <c r="P47" s="53"/>
-      <c r="Q47" s="54"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="L48" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="M48" s="39"/>
-      <c r="N48" s="40"/>
-      <c r="O48" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" s="50"/>
-      <c r="Q48" s="51"/>
-    </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="L49" s="29"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="31"/>
-      <c r="O49" s="52"/>
-      <c r="P49" s="53"/>
-      <c r="Q49" s="54"/>
-    </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="P35" s="51"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="53"/>
+      <c r="S35" s="54"/>
+    </row>
+    <row r="36" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="40" spans="2:19" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="42" spans="2:19" ht="33.6" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="43" spans="2:19" ht="26.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="44" spans="2:19" ht="25.8" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="45" spans="2:19" ht="26.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="46" spans="2:19" ht="43.2" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="47" spans="2:19" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.45">
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="L50" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="M50" s="39"/>
-      <c r="N50" s="40"/>
-      <c r="O50" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="P50" s="55"/>
-      <c r="Q50" s="56"/>
-    </row>
-    <row r="51" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.45">
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="21"/>
-      <c r="N51" s="22"/>
-      <c r="O51" s="45"/>
-      <c r="P51" s="21"/>
-      <c r="Q51" s="46"/>
-    </row>
-    <row r="52" spans="2:17" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -2720,7 +2936,7 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -2730,7 +2946,7 @@
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -2738,7 +2954,7 @@
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -2748,95 +2964,95 @@
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="X10:AA11"/>
+    <mergeCell ref="X8:AA9"/>
+    <mergeCell ref="X6:AA7"/>
+    <mergeCell ref="X4:AA5"/>
+    <mergeCell ref="O12:R13"/>
+    <mergeCell ref="O14:R15"/>
+    <mergeCell ref="O16:R17"/>
+    <mergeCell ref="O24:R25"/>
+    <mergeCell ref="O22:R23"/>
+    <mergeCell ref="O20:R21"/>
+    <mergeCell ref="O18:R19"/>
+    <mergeCell ref="L34:M35"/>
+    <mergeCell ref="L32:M33"/>
+    <mergeCell ref="L30:M31"/>
+    <mergeCell ref="L28:M29"/>
+    <mergeCell ref="N34:O35"/>
+    <mergeCell ref="N32:O33"/>
+    <mergeCell ref="J28:K29"/>
+    <mergeCell ref="N30:O31"/>
+    <mergeCell ref="N28:O29"/>
+    <mergeCell ref="B26:D27"/>
+    <mergeCell ref="B28:D29"/>
+    <mergeCell ref="B32:D33"/>
+    <mergeCell ref="P30:Q31"/>
+    <mergeCell ref="P28:Q29"/>
+    <mergeCell ref="E26:H27"/>
+    <mergeCell ref="E28:H29"/>
+    <mergeCell ref="E30:H31"/>
+    <mergeCell ref="E32:H33"/>
+    <mergeCell ref="L20:N21"/>
+    <mergeCell ref="U20:W21"/>
+    <mergeCell ref="U18:W19"/>
+    <mergeCell ref="U16:W17"/>
+    <mergeCell ref="U14:W15"/>
+    <mergeCell ref="U4:W5"/>
+    <mergeCell ref="U6:W7"/>
+    <mergeCell ref="U8:W9"/>
+    <mergeCell ref="U10:W11"/>
+    <mergeCell ref="L24:N25"/>
+    <mergeCell ref="L22:N23"/>
+    <mergeCell ref="R30:S31"/>
+    <mergeCell ref="R28:S29"/>
+    <mergeCell ref="P34:Q35"/>
+    <mergeCell ref="P32:Q33"/>
+    <mergeCell ref="R34:S35"/>
+    <mergeCell ref="R32:S33"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="U12:W13"/>
+    <mergeCell ref="U24:W25"/>
+    <mergeCell ref="U22:W23"/>
+    <mergeCell ref="X24:AA25"/>
+    <mergeCell ref="X22:AA23"/>
+    <mergeCell ref="X20:AA21"/>
+    <mergeCell ref="X14:AA15"/>
+    <mergeCell ref="X18:AA19"/>
+    <mergeCell ref="X16:AA17"/>
+    <mergeCell ref="X12:AA13"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="L10:N11"/>
+    <mergeCell ref="L8:N9"/>
+    <mergeCell ref="L6:N7"/>
+    <mergeCell ref="L12:N13"/>
+    <mergeCell ref="L14:N15"/>
+    <mergeCell ref="L18:N19"/>
+    <mergeCell ref="L16:N17"/>
+    <mergeCell ref="E6:H7"/>
+    <mergeCell ref="E8:H9"/>
+    <mergeCell ref="B4:D5"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="B8:D9"/>
+    <mergeCell ref="L4:N5"/>
+    <mergeCell ref="E4:H5"/>
+    <mergeCell ref="E10:H11"/>
+    <mergeCell ref="O4:R5"/>
+    <mergeCell ref="O6:R7"/>
+    <mergeCell ref="O8:R9"/>
+    <mergeCell ref="O10:R11"/>
     <mergeCell ref="B30:D31"/>
     <mergeCell ref="B14:D15"/>
     <mergeCell ref="B12:D13"/>
     <mergeCell ref="B10:D11"/>
-    <mergeCell ref="E14:G15"/>
-    <mergeCell ref="E12:G13"/>
-    <mergeCell ref="E10:G11"/>
-    <mergeCell ref="O4:Q5"/>
-    <mergeCell ref="O6:Q7"/>
-    <mergeCell ref="O10:Q11"/>
-    <mergeCell ref="O8:Q9"/>
-    <mergeCell ref="B4:D5"/>
-    <mergeCell ref="E4:G5"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="B8:D9"/>
-    <mergeCell ref="L4:N5"/>
-    <mergeCell ref="O12:Q13"/>
-    <mergeCell ref="O14:Q15"/>
-    <mergeCell ref="O16:Q17"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="L10:N11"/>
-    <mergeCell ref="L8:N9"/>
-    <mergeCell ref="L6:N7"/>
-    <mergeCell ref="O50:Q51"/>
-    <mergeCell ref="L38:N39"/>
-    <mergeCell ref="O42:Q43"/>
-    <mergeCell ref="O44:Q45"/>
-    <mergeCell ref="O46:Q47"/>
-    <mergeCell ref="O38:Q39"/>
-    <mergeCell ref="O40:Q41"/>
-    <mergeCell ref="L50:N51"/>
-    <mergeCell ref="L48:N49"/>
-    <mergeCell ref="O18:Q19"/>
-    <mergeCell ref="O22:Q23"/>
-    <mergeCell ref="O24:Q25"/>
-    <mergeCell ref="E24:G25"/>
-    <mergeCell ref="O48:Q49"/>
-    <mergeCell ref="O36:Q37"/>
-    <mergeCell ref="O30:Q31"/>
-    <mergeCell ref="O32:Q33"/>
-    <mergeCell ref="O34:Q35"/>
-    <mergeCell ref="O27:O28"/>
-    <mergeCell ref="O20:Q21"/>
-    <mergeCell ref="L20:N21"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="L46:N47"/>
-    <mergeCell ref="L44:N45"/>
-    <mergeCell ref="L42:N43"/>
-    <mergeCell ref="L40:N41"/>
-    <mergeCell ref="L12:N13"/>
-    <mergeCell ref="L14:N15"/>
-    <mergeCell ref="L30:N31"/>
-    <mergeCell ref="L32:N33"/>
-    <mergeCell ref="L34:N35"/>
-    <mergeCell ref="L36:N37"/>
-    <mergeCell ref="L24:N25"/>
-    <mergeCell ref="L22:N23"/>
-    <mergeCell ref="L18:N19"/>
-    <mergeCell ref="L16:N17"/>
     <mergeCell ref="B20:D21"/>
-    <mergeCell ref="E20:G21"/>
     <mergeCell ref="B22:D23"/>
-    <mergeCell ref="H40:I41"/>
-    <mergeCell ref="H38:I39"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="D42:E43"/>
-    <mergeCell ref="D40:E41"/>
-    <mergeCell ref="B26:D27"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="B28:D29"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="B32:D33"/>
-    <mergeCell ref="E32:G33"/>
-    <mergeCell ref="E22:G23"/>
     <mergeCell ref="B24:D25"/>
-    <mergeCell ref="F46:G47"/>
-    <mergeCell ref="F44:G45"/>
-    <mergeCell ref="F42:G43"/>
-    <mergeCell ref="F40:G41"/>
-    <mergeCell ref="H44:I45"/>
-    <mergeCell ref="H42:I43"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="D46:E47"/>
-    <mergeCell ref="D44:E45"/>
+    <mergeCell ref="E12:H13"/>
+    <mergeCell ref="E14:H15"/>
+    <mergeCell ref="E20:H21"/>
+    <mergeCell ref="E22:H23"/>
+    <mergeCell ref="E24:H25"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
